--- a/artfynd/A 1192-2023 artfynd.xlsx
+++ b/artfynd/A 1192-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120447404</v>
+        <v>120447448</v>
       </c>
       <c r="B2" t="n">
-        <v>58023</v>
+        <v>57822</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>102995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332426</v>
+        <v>332411</v>
       </c>
       <c r="R2" t="n">
-        <v>6550065</v>
+        <v>6550023</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120447448</v>
+        <v>120447253</v>
       </c>
       <c r="B3" t="n">
-        <v>57822</v>
+        <v>56532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102995</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,19 +848,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -869,13 +859,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332411</v>
+        <v>332454</v>
       </c>
       <c r="R3" t="n">
-        <v>6550023</v>
+        <v>6550095</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,22 +889,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120447253</v>
+        <v>120447404</v>
       </c>
       <c r="B4" t="n">
-        <v>56532</v>
+        <v>58023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,20 +937,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -983,9 +963,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,13 +984,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332454</v>
+        <v>332426</v>
       </c>
       <c r="R4" t="n">
-        <v>6550095</v>
+        <v>6550065</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,12 +1014,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Andreas Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 1192-2023 artfynd.xlsx
+++ b/artfynd/A 1192-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120447448</v>
+        <v>120447404</v>
       </c>
       <c r="B2" t="n">
-        <v>57822</v>
+        <v>58023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102995</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332411</v>
+        <v>332426</v>
       </c>
       <c r="R2" t="n">
-        <v>6550023</v>
+        <v>6550065</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120447253</v>
+        <v>120447448</v>
       </c>
       <c r="B3" t="n">
-        <v>56532</v>
+        <v>57822</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,9 +848,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,13 +869,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332454</v>
+        <v>332411</v>
       </c>
       <c r="R3" t="n">
-        <v>6550095</v>
+        <v>6550023</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,12 +899,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Andreas Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120447404</v>
+        <v>120447253</v>
       </c>
       <c r="B4" t="n">
-        <v>58023</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,20 +957,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,19 +983,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,13 +994,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332426</v>
+        <v>332454</v>
       </c>
       <c r="R4" t="n">
-        <v>6550065</v>
+        <v>6550095</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,22 +1024,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 1192-2023 artfynd.xlsx
+++ b/artfynd/A 1192-2023 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120447448</v>
+        <v>120447253</v>
       </c>
       <c r="B3" t="n">
-        <v>57822</v>
+        <v>56532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102995</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,19 +848,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -869,13 +859,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332411</v>
+        <v>332454</v>
       </c>
       <c r="R3" t="n">
-        <v>6550023</v>
+        <v>6550095</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,22 +889,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120447253</v>
+        <v>120447448</v>
       </c>
       <c r="B4" t="n">
-        <v>56532</v>
+        <v>57822</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,9 +963,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,13 +984,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332454</v>
+        <v>332411</v>
       </c>
       <c r="R4" t="n">
-        <v>6550095</v>
+        <v>6550023</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,12 +1014,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Andreas Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 1192-2023 artfynd.xlsx
+++ b/artfynd/A 1192-2023 artfynd.xlsx
@@ -948,12 +948,7 @@
         <v>120447253</v>
       </c>
       <c r="B4" t="n">
-        <v>56556</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,16 +973,15 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spillning</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>N Slängom, Dls</t>
